--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
@@ -26,9 +26,6 @@
     <t>产品主代码*</t>
   </si>
   <si>
-    <t>余额日期（yyyy-mm-dd）*</t>
-  </si>
-  <si>
     <t>科目号*</t>
   </si>
   <si>
@@ -63,6 +60,10 @@
   </si>
   <si>
     <t>原币发生额（借方）</t>
+  </si>
+  <si>
+    <t>余额日期*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -438,12 +439,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
-    <col min="2" max="2" width="27.08984375" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" customWidth="1"/>
-    <col min="4" max="4" width="13.36328125" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -451,28 +451,23 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B7">
-      <formula1>"01借方,02贷方"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -488,42 +483,42 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
@@ -121,7 +121,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -129,6 +129,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -435,11 +438,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" style="3" customWidth="1"/>
     <col min="3" max="3" width="13.36328125" customWidth="1"/>
     <col min="4" max="4" width="13.7265625" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
@@ -450,7 +453,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C1" t="s">
@@ -465,6 +468,12 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="E7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>产品主代码*</t>
   </si>
@@ -65,12 +65,24 @@
     <t>余额日期*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>数据状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,17 +94,27 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -121,7 +143,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -132,6 +154,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -438,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
@@ -449,30 +474,39 @@
     <col min="6" max="6" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="H1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:9">
       <c r="E7" s="3"/>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>产品主代码*</t>
   </si>
@@ -75,6 +75,10 @@
   </si>
   <si>
     <t>更新人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误信息</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
@@ -474,7 +478,7 @@
     <col min="6" max="6" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
@@ -496,17 +500,20 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="E7" s="3"/>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>产品主代码*</t>
   </si>
@@ -79,6 +79,10 @@
   </si>
   <si>
     <t>错误信息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -467,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
@@ -478,42 +482,45 @@
     <col min="6" max="6" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="E7" s="3"/>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6E5FF7-FB1A-4694-B245-D360B8C8D17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,71 +27,73 @@
     <t>产品主代码*</t>
   </si>
   <si>
+    <t>原币币种*</t>
+  </si>
+  <si>
+    <t>原币余额*</t>
+  </si>
+  <si>
+    <t>产品主代码</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>余额日期（yyyy-mm-dd）</t>
+  </si>
+  <si>
+    <t>科目号</t>
+  </si>
+  <si>
+    <t>原币币种</t>
+  </si>
+  <si>
+    <t>原币余额</t>
+  </si>
+  <si>
+    <t>原币发生额（贷方）</t>
+  </si>
+  <si>
+    <t>原币发生额（借方）</t>
+  </si>
+  <si>
+    <t>余额日期*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误信息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>科目号*</t>
-  </si>
-  <si>
-    <t>原币币种*</t>
-  </si>
-  <si>
-    <t>原币余额*</t>
-  </si>
-  <si>
-    <t>原币发生额（借方）*</t>
-  </si>
-  <si>
-    <t>产品主代码</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>余额日期（yyyy-mm-dd）</t>
-  </si>
-  <si>
-    <t>科目号</t>
-  </si>
-  <si>
-    <t>原币币种</t>
-  </si>
-  <si>
-    <t>原币余额</t>
-  </si>
-  <si>
-    <t>原币发生额（贷方）</t>
-  </si>
-  <si>
-    <t>原币发生额（借方）</t>
-  </si>
-  <si>
-    <t>余额日期*</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>错误信息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>科目名称*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,58 +473,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" customWidth="1"/>
-    <col min="4" max="4" width="13.7265625" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="23.1796875" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="23.21875" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="K1" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -531,51 +536,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.08984375" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -586,9 +591,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SubBalanceInfo.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25726"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6E5FF7-FB1A-4694-B245-D360B8C8D17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,23 +76,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>产品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>科目号*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>科目名称*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,20 +472,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.21875" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="17.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.375" customWidth="1"/>
+    <col min="4" max="4" width="13.75" customWidth="1"/>
     <col min="5" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="23.21875" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.25" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
@@ -494,16 +493,16 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>1</v>
@@ -521,10 +520,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
@@ -536,49 +535,49 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.109375" customWidth="1"/>
+    <col min="1" max="1" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -591,9 +590,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
